--- a/mlef_pipeline/results/OS_6/IO_ONLY/training_summary.xlsx
+++ b/mlef_pipeline/results/OS_6/IO_ONLY/training_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,803 +548,292 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RWD</t>
+          <t>RWD_FMRAD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6959114873634157</v>
+        <v>0.7097627304707966</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03461348488398852</v>
+        <v>0.05093273345247917</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6251574147980948</v>
+        <v>0.6279628596286779</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03921945599568459</v>
+        <v>0.03731290709896996</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6346698043713564</v>
+        <v>0.6425675850842441</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07151449864717946</v>
+        <v>0.07140368015312037</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6525167791023126</v>
+        <v>0.6424122468271448</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1128897976545978</v>
+        <v>0.08985279430838178</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6760489510489509</v>
+        <v>0.6466552315608919</v>
       </c>
       <c r="K2" t="n">
-        <v>0.08752794840986611</v>
+        <v>0.1242403290201428</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6006776958341639</v>
+        <v>0.6098969072164948</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5288461538461539</v>
+        <v>0.6037735849056604</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7454545454545455</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6276470588235292</v>
+        <v>0.5918367346938773</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1279914967450408</v>
+        <v>0.1778898812664993</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6362019914651493</v>
+        <v>0.4731182795698925</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9264705882352942</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="S2" t="n">
-        <v>0.32</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="T2" t="n">
         <v>11</v>
       </c>
       <c r="U2" t="n">
-        <v>892</v>
+        <v>418</v>
       </c>
       <c r="V2" t="n">
-        <v>159</v>
+        <v>86</v>
       </c>
       <c r="W2" t="n">
-        <v>93</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RWD_DP</t>
+          <t>RWD_FMRAD/rwd-only</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6720880172207606</v>
+        <v>0.655223173074524</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06336844916765672</v>
+        <v>0.05532433437866813</v>
       </c>
       <c r="D3" t="n">
-        <v>0.564252921307665</v>
+        <v>0.6122716280965279</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05929822087791441</v>
+        <v>0.04897220530970145</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5905582508524427</v>
+        <v>0.6258702369926176</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1647950845472102</v>
+        <v>0.07688676006022691</v>
       </c>
       <c r="H3" t="n">
-        <v>0.571409497029573</v>
+        <v>0.6299836525118622</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1621412286277697</v>
+        <v>0.1159072875303719</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7326388888888888</v>
+        <v>0.6941109205260149</v>
       </c>
       <c r="K3" t="n">
-        <v>0.173215061451501</v>
+        <v>0.1125259662783542</v>
       </c>
       <c r="L3" t="n">
-        <v>0.706766917293233</v>
+        <v>0.6137198856676194</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.5660377358490566</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.696969696969697</v>
       </c>
       <c r="O3" t="n">
-        <v>0.654885654885655</v>
+        <v>0.7183673469387755</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1928078329198009</v>
+        <v>0.1687412103994572</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6361746361746362</v>
+        <v>0.5649048625792812</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8108108108108109</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="T3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="U3" t="n">
-        <v>298</v>
+        <v>418</v>
       </c>
       <c r="V3" t="n">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="W3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RWD_DP/rwd-only</t>
+          <t>RWD_DP_FMRAD</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6828749103085385</v>
+        <v>0.8199279711884754</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0610804491655953</v>
+        <v>0.07008288820720265</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5780944903149369</v>
+        <v>0.7210377484927151</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06749541356681062</v>
+        <v>0.06703623776772093</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5698060849849718</v>
+        <v>0.725935101818841</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07755811663339893</v>
+        <v>0.1305551134530901</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6304198136267002</v>
+        <v>0.7560254284134881</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1601698656544395</v>
+        <v>0.126654172994184</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7899305555555556</v>
+        <v>0.6238095238095236</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1229802005885551</v>
+        <v>0.2362271422331147</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5964523281596452</v>
+        <v>0.5643243243243243</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="N4" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0.596673596673597</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1995111751313289</v>
+        <v>0.1997861414652553</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5776478232618583</v>
+        <v>0.5067319461444308</v>
       </c>
       <c r="R4" t="n">
-        <v>0.918918918918919</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.375</v>
       </c>
       <c r="T4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U4" t="n">
-        <v>298</v>
+        <v>134</v>
       </c>
       <c r="V4" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="W4" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RWD_FMRAD</t>
+          <t>RWD_DP_FMRAD/rwd-only</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7561192859942281</v>
+        <v>0.6256902761104443</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05171776711800247</v>
+        <v>0.0994486912655913</v>
       </c>
       <c r="D5" t="n">
-        <v>0.679189061707265</v>
+        <v>0.5146990136728943</v>
       </c>
       <c r="E5" t="n">
-        <v>0.055365010546508</v>
+        <v>0.1120432972303058</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7211374107433522</v>
+        <v>0.3349401776542389</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04824803963197</v>
+        <v>0.1396987753736023</v>
       </c>
       <c r="H5" t="n">
-        <v>0.673421527026502</v>
+        <v>0.8689883913764511</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1060551077961168</v>
+        <v>0.109314451062534</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5697916666666666</v>
+        <v>0.7428571428571427</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1510517345044612</v>
+        <v>0.1931160266988426</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5733333333333333</v>
+        <v>0.6125</v>
       </c>
       <c r="M5" t="n">
-        <v>0.65</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>0.54040404040404</v>
+        <v>0.9184782608695654</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1941745783209912</v>
+        <v>0.09218019594719479</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4522144522144522</v>
+        <v>0.5479166666666666</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6363636363636364</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U5" t="n">
-        <v>348</v>
+        <v>134</v>
       </c>
       <c r="V5" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="W5" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RWD_FMRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.6924323939145616</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.0556223897731084</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.6211891870713362</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.04615970204140817</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.6904302228554258</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.08120383570009425</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.6010658512487911</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.1748580182497886</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.1486510403081091</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.492202462380301</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.2916666666666667</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.7727272727272727</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.1537573369904</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.5090218423551757</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.9722222222222222</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.09090909090909091</v>
-      </c>
-      <c r="T6" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>348</v>
-      </c>
-      <c r="V6" t="n">
-        <v>64</v>
-      </c>
-      <c r="W6" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RWD_PYRAD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.5864259782170231</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.05776921275963987</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.543000409867494</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.05834780286192168</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.5648213001245179</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.06493350569251276</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.5449370785007195</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.1073588022528035</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.6026300743281875</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.1212160769469465</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.5520833333333333</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.6792452830188679</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.4242424242424243</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.5420168067226891</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.1892208204608089</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.5139964264443121</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.8235294117647058</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.2142857142857143</v>
-      </c>
-      <c r="T7" t="n">
-        <v>12</v>
-      </c>
-      <c r="U7" t="n">
-        <v>416</v>
-      </c>
-      <c r="V7" t="n">
-        <v>86</v>
-      </c>
-      <c r="W7" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RWD_PYRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.6288574021782978</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.05574029788603774</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.5735989771657345</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.04275354636069755</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.5536740916536709</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.1268770701335904</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.6561746935732737</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.1953045784091637</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.7024013722126928</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.1079033538731562</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.660541717707908</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.6037735849056604</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.7575757575757576</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.7237394957983194</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.1659599048750786</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.5577007459412022</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.4705882352941176</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="T8" t="n">
-        <v>7</v>
-      </c>
-      <c r="U8" t="n">
-        <v>416</v>
-      </c>
-      <c r="V8" t="n">
-        <v>86</v>
-      </c>
-      <c r="W8" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RWD_DP_FMRAD</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.8856184798807749</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.06299097580531665</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.7804232804232806</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.07016690389245098</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.7233410605621559</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.08853244551677929</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.8426470588235294</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1105682866863788</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.6372549019607843</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2785063524002793</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.5801217038539555</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.5144927536231885</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.2567426071480828</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.4024242424242425</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.3478260869565217</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="T9" t="n">
-        <v>9</v>
-      </c>
-      <c r="U9" t="n">
-        <v>105</v>
-      </c>
-      <c r="V9" t="n">
-        <v>23</v>
-      </c>
-      <c r="W9" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RWD_DP_FMRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.7261549925484352</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.09819713551443554</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.5875361820009244</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.08615502370850918</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.5095865932579929</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.09481074842436787</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.7052130467571643</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.1093049701864968</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.7745098039215685</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.2434411498822422</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.6919642857142857</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.7101449275362319</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.1871987763414953</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.5606060606060606</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.5217391304347826</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="T10" t="n">
-        <v>11</v>
-      </c>
-      <c r="U10" t="n">
-        <v>105</v>
-      </c>
-      <c r="V10" t="n">
-        <v>23</v>
-      </c>
-      <c r="W10" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RWD_DP_PYRAD</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.7068452380952382</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.09189732170543874</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.5966077031266905</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.05870492625629645</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.4481686055602464</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.09059669394888777</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.8719178969178969</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.05656858677113732</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.3904761904761904</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.2138609173169127</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.3845350052246604</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.2380952380952381</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.3532608695652173</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.2152450043861467</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.3541666666666666</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.2608695652173913</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="T11" t="n">
-        <v>6</v>
-      </c>
-      <c r="U11" t="n">
-        <v>132</v>
-      </c>
-      <c r="V11" t="n">
-        <v>31</v>
-      </c>
-      <c r="W11" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RWD_DP_PYRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.6552579365079364</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.09447203567508566</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.459629391202667</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.1304896593760232</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.2463133658567095</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.1913739588417729</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.9491582491582492</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.07408402137066371</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.7238095238095237</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.2174579973584225</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.6391534391534391</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.8641304347826089</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.1511581692003994</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.6313513513513513</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.5652173913043478</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="T12" t="n">
-        <v>11</v>
-      </c>
-      <c r="U12" t="n">
-        <v>132</v>
-      </c>
-      <c r="V12" t="n">
-        <v>31</v>
-      </c>
-      <c r="W12" t="n">
         <v>31</v>
       </c>
     </row>

--- a/mlef_pipeline/results/OS_6/IO_ONLY/training_summary.xlsx
+++ b/mlef_pipeline/results/OS_6/IO_ONLY/training_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,292 +548,803 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RWD_FMRAD</t>
+          <t>RWD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7097627304707966</v>
+        <v>0.7134783053567485</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05093273345247917</v>
+        <v>0.03418600650908721</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6279628596286779</v>
+        <v>0.641771965124167</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03731290709896996</v>
+        <v>0.03078777184434209</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6425675850842441</v>
+        <v>0.6304854547688474</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07140368015312037</v>
+        <v>0.05132065037918598</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6424122468271448</v>
+        <v>0.6927913990384912</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08985279430838178</v>
+        <v>0.09256762116090278</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6466552315608919</v>
+        <v>0.6842657342657343</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1242403290201428</v>
+        <v>0.08683976252292291</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6098969072164948</v>
+        <v>0.5947754061803122</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6037735849056604</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.7454545454545455</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5918367346938773</v>
+        <v>0.6505882352941179</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1778898812664993</v>
+        <v>0.1264658562880103</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4731182795698925</v>
+        <v>0.6120079811354979</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5428571428571428</v>
+        <v>0.9264705882352942</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.28</v>
       </c>
       <c r="T2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U2" t="n">
-        <v>418</v>
+        <v>892</v>
       </c>
       <c r="V2" t="n">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="W2" t="n">
-        <v>49</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RWD_FMRAD/rwd-only</t>
+          <t>RWD_DP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.655223173074524</v>
+        <v>0.6494618512317627</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05532433437866813</v>
+        <v>0.06364488923990064</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6122716280965279</v>
+        <v>0.5376391749683213</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04897220530970145</v>
+        <v>0.05756355386518905</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6258702369926176</v>
+        <v>0.4774608992628875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07688676006022691</v>
+        <v>0.1498527912121303</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6299836525118622</v>
+        <v>0.6732300915697472</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1159072875303719</v>
+        <v>0.1778896775887933</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6941109205260149</v>
+        <v>0.7048611111111112</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1125259662783542</v>
+        <v>0.1602689031789533</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6137198856676194</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5660377358490566</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.696969696969697</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7183673469387755</v>
+        <v>0.5426195426195426</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1687412103994572</v>
+        <v>0.1721613427569401</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5649048625792812</v>
+        <v>0.4252873563218391</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4857142857142857</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7857142857142857</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="U3" t="n">
-        <v>418</v>
+        <v>298</v>
       </c>
       <c r="V3" t="n">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="W3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RWD_DP_FMRAD</t>
+          <t>RWD_DP/rwd-only</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8199279711884754</v>
+        <v>0.7205453240851472</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07008288820720265</v>
+        <v>0.06030936278519572</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7210377484927151</v>
+        <v>0.6101160830424937</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06703623776772093</v>
+        <v>0.04587732665764111</v>
       </c>
       <c r="F4" t="n">
-        <v>0.725935101818841</v>
+        <v>0.5717615969672284</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1305551134530901</v>
+        <v>0.1114197794929952</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7560254284134881</v>
+        <v>0.7314738004918921</v>
       </c>
       <c r="I4" t="n">
-        <v>0.126654172994184</v>
+        <v>0.1239031040517662</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6238095238095236</v>
+        <v>0.6649305555555556</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2362271422331147</v>
+        <v>0.1826336194186908</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5643243243243243</v>
+        <v>0.5524956970740103</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6</v>
+        <v>0.1875</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.7442827442827447</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1997861414652553</v>
+        <v>0.165821357281865</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5067319461444308</v>
+        <v>0.5479204339963833</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.8648648648648649</v>
       </c>
       <c r="S4" t="n">
-        <v>0.375</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="T4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U4" t="n">
-        <v>134</v>
+        <v>298</v>
       </c>
       <c r="V4" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="W4" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>RWD_FMRAD</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.7097627304707966</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.05093273345247917</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.6279628596286779</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.03731290709896996</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6425675850842441</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.07140368015312037</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6424122468271448</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.08985279430838178</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6466552315608919</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1242403290201428</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6098969072164948</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.6037735849056604</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.5918367346938773</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1778898812664993</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.4731182795698925</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.5428571428571428</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="T5" t="n">
+        <v>11</v>
+      </c>
+      <c r="U5" t="n">
+        <v>418</v>
+      </c>
+      <c r="V5" t="n">
+        <v>86</v>
+      </c>
+      <c r="W5" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RWD_FMRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.655223173074524</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.05532433437866813</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6122716280965279</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.04897220530970145</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6258702369926176</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.07688676006022691</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6299836525118622</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1159072875303719</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6941109205260149</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1125259662783542</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6137198856676194</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5660377358490566</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.696969696969697</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.7183673469387755</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1687412103994572</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5649048625792812</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.4857142857142857</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>418</v>
+      </c>
+      <c r="V6" t="n">
+        <v>86</v>
+      </c>
+      <c r="W6" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.6310256151674061</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.05554167233217799</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5709263180561184</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.05506559058309731</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.62869209311041</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.06850133144691899</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5264940469998786</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.0522386637091276</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6237850200114351</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1210079029032579</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6160714285714286</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.7735849056603774</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.6890756302521008</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1642323583675632</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.5078605604921395</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="T7" t="n">
+        <v>12</v>
+      </c>
+      <c r="U7" t="n">
+        <v>416</v>
+      </c>
+      <c r="V7" t="n">
+        <v>86</v>
+      </c>
+      <c r="W7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6493923961274708</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.05359857786588618</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6143202036632016</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0526569138980758</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5884278589260025</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.07838277315210648</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6816220354189421</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.06091718225448237</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6357918810748998</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1187009636688353</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5449735449735449</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.4905660377358491</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.7216386554621848</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.1684228683069535</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5897435897435898</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.9705882352941176</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="T8" t="n">
+        <v>11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>416</v>
+      </c>
+      <c r="V8" t="n">
+        <v>86</v>
+      </c>
+      <c r="W8" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RWD_DP_FMRAD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.8199279711884754</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.07008288820720265</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7210377484927151</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.06703623776772093</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.725935101818841</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1305551134530901</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7560254284134881</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.126654172994184</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6238095238095236</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2362271422331147</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5643243243243243</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.6086956521739131</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.1997861414652553</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.5067319461444308</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="T9" t="n">
+        <v>12</v>
+      </c>
+      <c r="U9" t="n">
+        <v>134</v>
+      </c>
+      <c r="V9" t="n">
+        <v>31</v>
+      </c>
+      <c r="W9" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>RWD_DP_FMRAD/rwd-only</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B10" t="n">
         <v>0.6256902761104443</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C10" t="n">
         <v>0.0994486912655913</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D10" t="n">
         <v>0.5146990136728943</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E10" t="n">
         <v>0.1120432972303058</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F10" t="n">
         <v>0.3349401776542389</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G10" t="n">
         <v>0.1396987753736023</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H10" t="n">
         <v>0.8689883913764511</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I10" t="n">
         <v>0.109314451062534</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J10" t="n">
         <v>0.7428571428571427</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K10" t="n">
         <v>0.1931160266988426</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L10" t="n">
         <v>0.6125</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M10" t="n">
         <v>0.4761904761904762</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N10" t="n">
         <v>0.9</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O10" t="n">
         <v>0.9184782608695654</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P10" t="n">
         <v>0.09218019594719479</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q10" t="n">
         <v>0.5479166666666666</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R10" t="n">
         <v>0.391304347826087</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T10" t="n">
         <v>8</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U10" t="n">
         <v>134</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V10" t="n">
         <v>31</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W10" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7460317460317462</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.08585472414431017</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6130175614276847</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.09901174382309101</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5162886605998062</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1122646097272338</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7958106708106708</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1051897186363269</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.3857142857142857</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.203430577997282</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3541666666666666</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.451086956521739</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.2243230497488631</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3845350052246604</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3043478260869565</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="T11" t="n">
+        <v>14</v>
+      </c>
+      <c r="U11" t="n">
+        <v>132</v>
+      </c>
+      <c r="V11" t="n">
+        <v>31</v>
+      </c>
+      <c r="W11" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.6408730158730159</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0954486914161955</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.3324041588384704</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.09793777764280798</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2438795853269538</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.3393676883796611</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7755892255892255</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.339955101990152</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6952380952380952</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.2058262567847242</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6198439241917503</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.9184782608695654</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.09243390833046111</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.7479674796747967</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="T12" t="n">
+        <v>11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>132</v>
+      </c>
+      <c r="V12" t="n">
+        <v>31</v>
+      </c>
+      <c r="W12" t="n">
         <v>31</v>
       </c>
     </row>
